--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_277_Germany_North_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_277_Germany_North_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R2ef7c44858944378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R808b9719c499427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rd052b0b22f0e44de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf9311d3b6bc14007"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6921b10742144a77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra2217f26c1024946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7115fb41aada4dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9266fc048cbb421b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc25c04955e2244e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R24ad12986f5b4854"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb2a0612f496e4c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R51bbb936f0f9400d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ277CommercialTable" displayName="EEZ277CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ277CommercialTable" displayName="EEZ277CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ277FunctionalTable" displayName="EEZ277FunctionalTable" ref="A1:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O26"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ277FunctionalTable" displayName="EEZ277FunctionalTable" ref="A1:E26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E26"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ277ValidationTable" displayName="EEZ277ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ277ValidationTable" displayName="EEZ277ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -12821,7 +12775,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc737236d4b0a4957"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91b02f34071d4205"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12831,20 +12785,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12852,714 +12796,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3.2766487251</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3.2766487251</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$182,A2,'Species'!$U$2:$U$182))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>422.1141251165953</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>422.1141251165953</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2714.4611821042004</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.233531677504611</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1712.1100537124933</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2714.4611821042004</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1820.2034633471312</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$182,A3,'Species'!$U$2:$U$182))</x:f>
-        <x:v>4940871.644787413</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.233531677504611</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1712.1100537124933</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4647456.2802929</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>293415.3644945128</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0631346153246697</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.06313461532466974</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10679.1435600053</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1727448859983354</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>148.84864516111568</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10679.1435600053</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>155.39656305310294</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$182,A4,'Species'!$U$2:$U$182))</x:f>
-        <x:v>1659502.2055755015</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1727448859983354</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>148.84864516111568</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1589576.0503878426</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>69926.15518765897</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0439904433453169</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.04399044334531688</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>12655.727672235202</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.349269815515198</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>223.49603125020096</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>12655.727672235202</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>344.3613770830682</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$182,A5,'Species'!$U$2:$U$182))</x:f>
-        <x:v>4358143.809199207</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.349269815515198</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>223.49603125020096</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2828504.907327912</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1529638.9018712956</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.5407941481410916</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.5407941481410917</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>38869.299298218706</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.111357032177674</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>129.22812175166408</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>38869.299298218706</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>140.00276208514842</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$182,A6,'Species'!$U$2:$U$182))</x:f>
-        <x:v>5441809.262064939</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.111357032177674</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>129.22812175166408</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5023006.542112078</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>418802.7199528618</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0833769011530618</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.08337690115306187</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5410.2109113497</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0046656054371854</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.108008662534978</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5410.2109113497</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.86268663810095</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$182,A7,'Species'!$U$2:$U$182))</x:f>
-        <x:v>58769.42577602635</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0046656054371854</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.108008662534978</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>54686.45875806402</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4082.967017962328</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.074661389870308</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.07466138987030783</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>21745.3675029481</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2642591065808935</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>183.76343765038246</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>21745.3675029481</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>211.3029022777135</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$182,A8,'Species'!$U$2:$U$182))</x:f>
-        <x:v>4594859.264468409</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2642591065808935</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>183.76343765038246</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3996003.4853126556</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>598855.7791557536</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1498636778863816</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1498636778863815</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>788.0168164853</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.580376359289623</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>380.5190109827265</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>788.0168164853</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>454.6797247903377</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$182,A9,'Species'!$U$2:$U$182))</x:f>
-        <x:v>358295.2692496942</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.580376359289623</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>380.5190109827265</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>299855.37964674307</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>58439.88960295112</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1948935839396932</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.1948935839396933</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>26.230854746</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3750755901276643</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>237.178648558222</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>26.230854746</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>258.92392677799745</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$182,A10,'Species'!$U$2:$U$182))</x:f>
-        <x:v>6791.79591357759</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3750755901276643</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>237.178648558222</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6221.398679183303</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>570.3972343942869</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0916831188303084</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09168311883030847</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>732.4664817796</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.829086435499712</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>674.6622890617087</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>732.4664817796</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>714.1833493370159</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$182,A11,'Species'!$U$2:$U$182))</x:f>
-        <x:v>523115.3652344551</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.829086435499712</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>674.6622890617087</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>494167.51325840136</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>28947.85197605373</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0585790267457684</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.058579026745768356</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>310.1165036306</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.975468409163648</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>945.0796442905248</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>310.1165036306</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1030.953705321945</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$182,A12,'Species'!$U$2:$U$182))</x:f>
-        <x:v>319715.7584994535</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.975468409163648</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>945.0796442905248</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>293084.7949398287</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>26630.963559624797</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0908643642366103</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.09086436423661018</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.0789655333</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.45</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2818.382931264455</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.0789655333</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2818.382931264455</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$182,A13,'Species'!$U$2:$U$182))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>222.55511121091493</x:v>
       </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.45</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2818.382931264455</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>222.55511121091493</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc17c497ec7794ae2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5823908f9af14dc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13569,20 +13049,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13590,1416 +13060,497 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>95.3113583071</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.157778130448591</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1438.063721884521</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>95.3113583071</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1543.3110698305998</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$182,A2,'Species'!$U$2:$U$182))</x:f>
-        <x:v>147095.07435593812</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.157778130448591</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1438.063721884521</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>137063.8066649774</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>10031.267690960725</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0731868458569809</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.07318684585698085</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>101.9346228809</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.440994126735892</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2760.5405232725816</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>101.9346228809</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2766.1793248537874</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$182,A3,'Species'!$U$2:$U$182))</x:f>
-        <x:v>281969.4462999134</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.440994126735892</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2760.5405232725816</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>281394.6571872329</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>574.7891126804752</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0020426440161514</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0020426440161513976</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.0006411651</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.92</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>831.7637711026708</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.0006411651</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>831.7637711026707</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$182,A4,'Species'!$U$2:$U$182))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>0.533297901475421</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.92</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>0.533297901475421</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>877.6708757613001</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.096844991949822</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1249.8128683594211</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>877.6708757613001</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1255.8344920383875</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$182,A5,'Species'!$U$2:$U$182))</x:f>
-        <x:v>1102209.358438579</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.096844991949822</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1249.8128683594211</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1096924.3547107556</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5285.003727823263</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0048180202263963</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.004818020226396421</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>231.90217306579999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.166850295907167</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1468.4200165971763</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>231.90217306579999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1745.5066062750657</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$182,A6,'Species'!$U$2:$U$182))</x:f>
-        <x:v>404786.7750958975</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.166850295907167</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1468.4200165971763</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>340529.79282220325</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>64256.982273694244</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1886970938464816</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.18869709384648167</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7069.4761115643005</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.360225880345199</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>229.20594629089462</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7069.4761115643005</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>374.1210996801628</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$182,A7,'Species'!$U$2:$U$182))</x:f>
-        <x:v>2644840.1770210774</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.360225880345199</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>229.20594629089462</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1620365.9619319695</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1024474.2150891079</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.632248664287926</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6322486642879259</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.8164988606999999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.0246269139429796</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1058.3441508834997</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.8164988606999999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1192.8189237981892</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$182,A8,'Species'!$U$2:$U$182))</x:f>
-        <x:v>973.9352923026215</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.0246269139429796</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1058.3441508834997</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>864.1367934248863</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>109.79849887773526</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.127061478822773</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.12706147882277313</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>98.9764136209</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.842056354996752</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>695.1145113079685</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>98.9764136209</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>781.4226175705913</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$182,A9,'Species'!$U$2:$U$182))</x:f>
-        <x:v>77342.40820939321</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.842056354996752</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>695.1145113079685</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>68799.94138510726</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>8542.466824285948</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1241638677636299</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12416386776362993</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>152.36237718629997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.3620788224381384</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>230.18595563528066</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>152.36237718629997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>233.96729969920634</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$182,A10,'Species'!$U$2:$U$182))</x:f>
-        <x:v>35647.81396603056</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.3620788224381384</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>230.18595563528066</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>35071.67939549154</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>576.1345705390195</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0164273448112406</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.016427344811240533</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>163.0093404412</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.099788906208498</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1258.3136454139992</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>163.0093404412</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1287.319395504434</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$182,A11,'Species'!$U$2:$U$182))</x:f>
-        <x:v>209845.0855983421</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.099788906208498</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1258.3136454139992</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>205116.87740709804</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>4728.208191244048</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0230512878852964</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.023051287885296312</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>2643.3128459027002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.1243503122242378</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>133.15280269916468</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>2643.3128459027002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>157.85494695669328</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$182,A12,'Species'!$U$2:$U$182))</x:f>
-        <x:v>417260.0090799167</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.1243503122242378</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>133.15280269916468</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>351964.51384264976</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>65295.495237266936</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1855172685575288</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.18551726855752884</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>76.4107887098</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.459993781057125</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2883.990205114541</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>76.4107887098</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2884.016599181309</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$182,A13,'Species'!$U$2:$U$182))</x:f>
-        <x:v>220369.98299559898</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.459993781057125</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2883.990205114541</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>220367.96620413996</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>2.016791459027445</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0000091519266332</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.00000915192663328921</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.16500144749999998</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.08</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1202.2644346174131</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.16500144749999998</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$182,A14,'Species'!$U$2:$U$182))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>198.37537198964225</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.08</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1202.2644346174131</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>198.37537198964225</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1494.9523835993</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.321344430004067</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>2095.7739120323813</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1494.9523835993</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>2196.423902032767</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$182,A15,'Species'!$U$2:$U$182))</x:f>
-        <x:v>3283549.1477383603</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.321344430004067</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>2095.7739120323813</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>3133082.205278038</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>150466.9424603223</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0480252137038866</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.04802521370388667</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>21123.1712981365</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3052748582361304</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>201.9644160728746</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>21123.1712981365</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>216.11151221327032</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$182,A16,'Species'!$U$2:$U$182))</x:f>
-        <x:v>4564960.491980228</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3052748582361304</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>201.9644160728746</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>4266128.956835443</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>298831.5351447845</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0700474688337724</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.07004746883377236</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>11201.298663064399</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.394189807056085</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>247.85050438989848</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>11201.298663064399</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>253.48085526376653</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$182,A17,'Species'!$U$2:$U$182))</x:f>
-        <x:v>2839314.7651784485</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.394189807056085</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>247.85050438989848</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2776247.523462407</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>63067.241716041695</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0227167214677555</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.022716721467755573</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4.6251092018</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3342161141491347</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>215.881841575615</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4.6251092018</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>223.41651574051417</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$182,A18,'Species'!$U$2:$U$182))</x:f>
-        <x:v>1033.3257827855466</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3342161141491347</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>215.881841575615</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>998.4770919729067</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>34.848690812639916</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.034901843109672</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.03490184310967199</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>6625.894471788699</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.1428321412317177</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>13.894155056848293</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>6625.894471788699</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>21.725413371645725</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$182,A19,'Species'!$U$2:$U$182))</x:f>
-        <x:v>143950.29635651168</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.1428321412317177</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>13.894155056848293</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>92061.2051813461</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>51889.09117516558</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.5636368877960292</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.563636887796029</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>8035.830714102601</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.188663837389951</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>154.40588089279808</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>8035.830714102601</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>154.5879002049525</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$182,A20,'Species'!$U$2:$U$182))</x:f>
-        <x:v>1242242.196495585</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.188663837389951</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>154.40588089279808</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1240779.5201164146</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>1462.6763791702688</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0011788366550676</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.0011788366550674813</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.0000033116</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.08</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>120.22644346174131</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.0000033116</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$182,A21,'Species'!$U$2:$U$182))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>0.0003981418901679026</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.08</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>120.22644346174131</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>0.0003981418901679026</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>28234.082952607798</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.0101329171953375</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>102.36062222571275</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>28234.082952607798</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>102.3664528389143</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$182,A22,'Species'!$U$2:$U$182))</x:f>
-        <x:v>2890222.9210181204</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.0101329171953375</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>102.36062222571275</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>2890058.299001323</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>164.62201679730788</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0000569614865051</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.00005696148650502795</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>68.80944279539999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.1102739031719824</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>128.90622880898883</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>68.80944279539999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>128.9714435049621</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$182,A23,'Species'!$U$2:$U$182))</x:f>
-        <x:v>8874.453164094852</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.1102739031719824</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>128.90622880898883</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>8869.965777202859</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>4.487386891993083</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0005059080276866</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.0005059080276866839</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>5586.2515606709</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.335404768846385</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>216.47351488247543</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>5586.2515606709</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>306.7000498581852</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$182,A24,'Species'!$U$2:$U$182))</x:f>
-        <x:v>1713303.6321781299</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.335404768846385</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>216.47351488247543</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>1209275.5103561438</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>504028.12182198605</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.4168017275678928</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.41680172756789285</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>22.719974968</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.8164175750369163</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>655.2659107921177</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>22.719974968</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>657.4503826900149</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$182,A25,'Species'!$U$2:$U$182))</x:f>
-        <x:v>14937.256237419157</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.8164175750369163</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>655.2659107921177</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>14887.625090580634</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>49.63114683852291</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.0033337182080118</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.0033337182080118623</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>25.410774600499998</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.839812387040657</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>691.5321680799275</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>25.410774600499998</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>692.2657310081697</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$182,A26,'Species'!$U$2:$U$182))</x:f>
-        <x:v>17591.008454298964</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.839812387040657</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>691.5321680799275</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>17572.368052074118</x:v>
       </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>18.640402224846184</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.001060779182954</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.0010607791829540015</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G26">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O26">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9ce0de2b0e144ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263dbc0959b74199"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15174,7 +13725,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -15273,7 +13824,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>22262518.470005006</x:v>
+        <x:v>19233207.47995193</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15287,7 +13838,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>22262518.47000501</x:v>
+        <x:v>20008624.253656026</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15301,7 +13852,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-3029310.99005308</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15315,7 +13866,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-2253894.2163489833</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -15326,9 +13877,9 @@
         <x:v>EEZ_277</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -15340,47 +13891,19 @@
         <x:v>EEZ_277</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_277</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_277</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafbf54245f0349c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb5371e4bb24aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15427,7 +13950,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
